--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-16.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-16.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,52 +486,27 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Stake_Sugerida_R$</t>
+          <t>Placar</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Risco_Red_R$</t>
+          <t>Resultado</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Placar</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Origem</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>1/0</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>P/L</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Lucro_Green_R$</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>PnL_u</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>PnL_R$</t>
+          <t>Liquidez_Lay</t>
         </is>
       </c>
     </row>
@@ -543,76 +518,65 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BOSNIA 1</t>
+          <t>Ukrainian Cup</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sloga Doboj x Borac Banja Luka</t>
+          <t>Kulikiv-Bilka FC x Veres Rivne</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Kulikiv-Bilka FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Match Odds (Draw)</t>
-        </is>
-      </c>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>LAY</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="K2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="L2" t="n">
-        <v>22.73</v>
-      </c>
-      <c r="M2" t="n">
-        <v>100</v>
+        <v>1.53</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -622,76 +586,65 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>AFC Champions League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia x CSKA Sofia</t>
+          <t>Port FC x Kobe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Kobe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Match Odds (Home)</t>
-        </is>
-      </c>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>LAY</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="K3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="L3" t="n">
-        <v>13.16</v>
-      </c>
-      <c r="M3" t="n">
-        <v>100</v>
+        <v>1.58</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1483</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -701,76 +654,65 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SERBIA 2</t>
+          <t>Greek Cup</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FK Proleter Zrenjanin x FK Backa Topola</t>
+          <t>Aris x Marko</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Proleter Zrenjanin</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FK Backa Topola</t>
+          <t>Marko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Over 4.5 FT</t>
-        </is>
-      </c>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>LAY</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M4" t="n">
-        <v>100</v>
+        <v>1.21</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -780,76 +722,65 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GERMANY 3</t>
+          <t>Czech Cup</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hansa Rostock x Stuttgart II</t>
+          <t>Vitkovice x SK Artis Brno</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Vitkovice</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Correct Score (2x2)</t>
-        </is>
-      </c>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>LAY</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>18</v>
+        <v>6.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="M5" t="n">
-        <v>100</v>
+        <v>1.35</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>162</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -859,76 +790,65 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>Czech Cup</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Deportivo x Sevilla</t>
+          <t>Kraluv Dvur x FC Zbrojovka Brno</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Kraluv Dvur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>FC Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Correct Score (2x2)</t>
-        </is>
-      </c>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>LAY</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="M6" t="n">
-        <v>100</v>
+        <v>1.23</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -938,83 +858,64 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARGENTINA 2</t>
+          <t>Turkish Cup</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>San Martin S.J. x Tristan Suarez</t>
+          <t>Bucaspor x Gaziemir GOG Sor Yat AS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>San Martin S.J.</t>
+          <t>Bucaspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tristan Suarez</t>
+          <t>Gaziemir GOG Sor Yat AS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lay 3x0 Top 3 (Aprovado)</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Correct Score (3x0)</t>
-        </is>
-      </c>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>LAY</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>7.69</v>
-      </c>
-      <c r="M7" t="n">
-        <v>200</v>
+        <v>1.12</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>coletor (KO-10)</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>🟢 GREEN</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.0371</v>
-      </c>
-      <c r="U7" t="n">
-        <v>7.42</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8">
@@ -1025,76 +926,65 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EUROPA LEAGUE</t>
+          <t>Czech Cup</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Olympiakos x Jagiellonia Bialystock</t>
+          <t>Vitkovice x SK Artis Brno</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Vitkovice</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jagiellonia Bialystock</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Match Odds (Draw)</t>
-        </is>
-      </c>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>LAY</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L8" t="n">
-        <v>20.41</v>
-      </c>
-      <c r="M8" t="n">
-        <v>100</v>
+        <v>1.35</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1104,76 +994,65 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>Czech Cup</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Portuguesa FC x Estudiantes de Merida</t>
+          <t>FK Pribram x Hradec Kralove</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Portuguesa FC</t>
+          <t>FK Pribram</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida</t>
+          <t>Hradec Kralove</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Correct Score (2x2)</t>
-        </is>
-      </c>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>LAY</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18.5</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="M9" t="n">
-        <v>100</v>
+        <v>1.56</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>172</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1183,81 +1062,1084 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>COPA LIBERTADORES</t>
+          <t>Danish Cup</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Corinthians x Estudiantes</t>
+          <t>Naesby x AC Horsens</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Naesby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lay 3x0 Top 3 (Aprovado)</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Correct Score (3x0)</t>
-        </is>
-      </c>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>LAY</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>28</v>
+        <v>6.6</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="M10" t="n">
-        <v>200</v>
+        <v>1.4</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Danish Cup</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Horsholm Usserod IK x Aarhus Fremad</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Horsholm Usserod IK</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Aarhus Fremad</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Danish Cup</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Naesby x AC Horsens</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Naesby</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AC Horsens</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Greek Cup</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Kifisia x Panathinaikos</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Slovenian 2 SNL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Triglav x Brezice</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Triglav</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Brezice</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Norwegian Cup</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Gamle Oslo x Lyn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Gamle Oslo</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lyn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Norwegian Cup</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Vindbjart x Start</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Vindbjart</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Norwegian Cup</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Kjelsas x Ham-Kam</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Kjelsas</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ham-Kam</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Lokomotiv Sofia x CSKA Sofia</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Lokomotiv Sofia</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CSKA Sofia</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Norwegian Cup</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Kjelsas x Ham-Kam</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Kjelsas</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ham-Kam</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Norwegian Cup</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Jerv x Egersund</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Jerv</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Egersund</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Slovakian Cup</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FC Nitra x Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FC Nitra</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Atletico Madrid x Osasuna</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>11432</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Uruguayan Cup</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Progreso x Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AFC Champions League Two</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Al Rayyan x Al Faisaly SC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Al Rayyan</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Al Faisaly SC</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Olympiakos x Jagiellonia Bialystock</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Olympiakos</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Jagiellonia Bialystock</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>2672</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-16.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-16.xlsx
@@ -558,15 +558,19 @@
       <c r="K2" t="n">
         <v>1.53</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0x1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -626,15 +630,19 @@
       <c r="K3" t="n">
         <v>1.58</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -694,15 +702,19 @@
       <c r="K4" t="n">
         <v>1.21</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2x4</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -762,15 +774,19 @@
       <c r="K5" t="n">
         <v>1.35</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0x3</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -830,15 +846,19 @@
       <c r="K6" t="n">
         <v>1.23</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0x3</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -898,15 +918,19 @@
       <c r="K7" t="n">
         <v>1.12</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0x4</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -966,15 +990,19 @@
       <c r="K8" t="n">
         <v>1.35</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0x3</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1034,15 +1062,19 @@
       <c r="K9" t="n">
         <v>1.56</v>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1102,15 +1134,19 @@
       <c r="K10" t="n">
         <v>1.4</v>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2x3</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1170,15 +1206,19 @@
       <c r="K11" t="n">
         <v>1.35</v>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🔴 RED</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1238,15 +1278,19 @@
       <c r="K12" t="n">
         <v>1.4</v>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2x3</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1306,15 +1350,19 @@
       <c r="K13" t="n">
         <v>1.45</v>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1374,15 +1422,19 @@
       <c r="K14" t="n">
         <v>1.34</v>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2x1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1442,15 +1494,19 @@
       <c r="K15" t="n">
         <v>1.25</v>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1x3</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1510,15 +1566,19 @@
       <c r="K16" t="n">
         <v>1.2</v>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2x3</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1578,15 +1638,19 @@
       <c r="K17" t="n">
         <v>1.39</v>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0x2</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1646,15 +1710,19 @@
       <c r="K18" t="n">
         <v>1.47</v>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0x2</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1714,15 +1782,19 @@
       <c r="K19" t="n">
         <v>1.39</v>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0x2</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1782,15 +1854,19 @@
       <c r="K20" t="n">
         <v>1.52</v>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1850,15 +1926,19 @@
       <c r="K21" t="n">
         <v>1.21</v>
       </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1x3</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1918,15 +1998,19 @@
       <c r="K22" t="n">
         <v>1.34</v>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>4x0</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1986,15 +2070,19 @@
       <c r="K23" t="n">
         <v>1.33</v>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1x0</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2057,12 +2145,12 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>SEM_PLACAR</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>⚪ SEM_PLACAR</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2122,15 +2210,19 @@
       <c r="K25" t="n">
         <v>1.36</v>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2x1</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
